--- a/data/trans_orig/P6905-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6905-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>50557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34302</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>50145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61841</t>
+          <t>61176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80866</t>
+          <t>82214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31117</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49498</t>
+          <t>49201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>24425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>36716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19061</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52853</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51614</t>
+          <t>52409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37408</t>
+          <t>37132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60374</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48416</t>
+          <t>47621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68307</t>
+          <t>68050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55942</t>
+          <t>57163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78908</t>
+          <t>79184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68769</t>
+          <t>70268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64540</t>
+          <t>64510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95514</t>
+          <t>94477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132060</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159633</t>
+          <t>158968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>33619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155261</t>
+          <t>156298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186235</t>
+          <t>186265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>44797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92912</t>
+          <t>92483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111340</t>
+          <t>111579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141892</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90168</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232061</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256786</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330413</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129953</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144119</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>446</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460366</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>435641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>141892</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>120280</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>163652</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>90168</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>77154</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>104241</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>40,96%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>35,05%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>232061</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>209046</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>259159</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>30,19%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>37,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>330413</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>308653</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>352025</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>69,96%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>129953</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>115880</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>142967</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>59,04%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>460366</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>433268</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>483381</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>62,57%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012 (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>26887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29160</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48937</t>
+          <t>48361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17551</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30375</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50391</t>
+          <t>50967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70168</t>
+          <t>70952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36691</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>50988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66717</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26267</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69276</t>
+          <t>69787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88860</t>
+          <t>89658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58086</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80569</t>
+          <t>80962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98474</t>
+          <t>99046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37398</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53364</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124076</t>
+          <t>122936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147550</t>
+          <t>148028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>37954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45580</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>63636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84545</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172594</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240802</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126786</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>348</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367588</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387438</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325347</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325347</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325347</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540182</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540182</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540182</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>84545</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>69651</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>102071</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>88049</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>74043</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>103828</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>172594</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>150211</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>195919</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>36,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>240802</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>223276</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>255696</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>74,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>78,59%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126786</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>111007</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>140792</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>59,02%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>65,53%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>367588</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>344263</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>389971</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>68,05%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>72,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>325347</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>325347</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>325347</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>214835</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>214835</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>214835</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>540182</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>540182</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>540182</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>24169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44731</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19739</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33873</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24444</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68008</t>
+          <t>68676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>30650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44776</t>
+          <t>44055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>28136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>58735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63170</t>
+          <t>63092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29261</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47607</t>
+          <t>47216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54312</t>
+          <t>56083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83652</t>
+          <t>84598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>93478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114672</t>
+          <t>114480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36470</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54816</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137294</t>
+          <t>136348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166634</t>
+          <t>164863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50067</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41481</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57288</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33736</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>65575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87357</t>
+          <t>87156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95064</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89574</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104549</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184638</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162076</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>235</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254937</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126724</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>355</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381661</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358143</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>404223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>95064</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>80193</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>114490</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>89574</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>75682</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>104613</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>41,41%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>34,99%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>48,37%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>184638</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>160012</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>206249</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>254937</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>235511</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>269808</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>67,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126724</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>111685</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>140616</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>58,59%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>51,63%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>65,01%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>381661</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>360050</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>406287</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>67,4%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>32572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32566</t>
+          <t>32491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51376</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>40260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>54848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72540</t>
+          <t>72615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43622</t>
+          <t>43929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32615</t>
+          <t>31978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55011</t>
+          <t>55467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73123</t>
+          <t>72789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21087</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27154</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37436</t>
+          <t>36264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49208</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>64680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37894</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>42273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75087</t>
+          <t>74000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95324</t>
+          <t>93215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117994</t>
+          <t>117954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62912</t>
+          <t>63485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80105</t>
+          <t>79732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163889</t>
+          <t>164976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192622</t>
+          <t>191580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50472</t>
+          <t>51841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>23304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60919</t>
+          <t>60637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34785</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>46442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76775</t>
+          <t>75406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>111611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117497</t>
+          <t>117779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156029</t>
+          <t>155112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62196</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82181</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191425</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>217349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>264</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261956</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>238416</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>270111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>585</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500372</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>534899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>77549</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>99292</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>113876</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>82775</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>133288</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>37,83%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>191425</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>161060</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>218917</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>261956</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>240213</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>278767</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>77,16%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>82,11%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>238416</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>219004</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>269517</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>67,68%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>62,17%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>500372</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>472880</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>530737</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>72,33%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>76,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
